--- a/TIA-Project-Tracker.xlsx
+++ b/TIA-Project-Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\TIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B504768B-F894-44B0-92F7-9F1BA8A5E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0C7E5C-DD83-47F3-9C72-5AD0478EA7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="0" windowWidth="19180" windowHeight="10080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Acceptance Criteria'!$A$1:$F$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Requirements!$A$1:$F$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Task Tracker'!$A$1:$P$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Task Tracker'!$A$1:$P$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="1090">
   <si>
     <t>TIA Enterprise - delivery dashboard</t>
   </si>
@@ -1084,6 +1084,93 @@
     <t>T-047</t>
   </si>
   <si>
+    <t>Azure DevOps: service-hook receiver, one PR comment thread updated in place (closed), advisory PR status (notApplicable), manual publish</t>
+  </si>
+  <si>
+    <t>Basic-auth service hooks compared in constant time; created/updated events queued per tenant (organisation-to-tenant mapping via the installation table); PAT only ever sent to dev.azure.com, *.visualstudio.com or the configured Azure DevOps Server; permanent vs transient failures; comment names only the PR's repository.</t>
+  </si>
+  <si>
+    <t>FR-001 FR-039</t>
+  </si>
+  <si>
+    <t>tia/ado.py, tia/api.py, tia/analysis_service.py</t>
+  </si>
+  <si>
+    <t>tests/test_ado.py (25) against an Azure DevOps REST stand-in, real git remotes and PostgreSQL</t>
+  </si>
+  <si>
+    <t>NOT verified against a real Azure DevOps organisation; no permission mirroring from Azure DevOps (repositories restricted until granted).</t>
+  </si>
+  <si>
+    <t>T-048</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>Container image, Docker Compose file and Helm chart (non-root, read-only, secrets from files, migration hook, network policy)</t>
+  </si>
+  <si>
+    <t>deploy/Dockerfile, deploy/docker-compose.yml, deploy/helm/tia; a CI job builds the image and validates the Compose file.</t>
+  </si>
+  <si>
+    <t>PL-009</t>
+  </si>
+  <si>
+    <t>deploy/</t>
+  </si>
+  <si>
+    <t>tests/test_deploy.py (14) static checks only</t>
+  </si>
+  <si>
+    <t>NEVER built, started or installed: no Docker or Kubernetes on the development machine; the CI container job has never run.</t>
+  </si>
+  <si>
+    <t>T-049</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>Knowledge Fabric V2.5 adapter: finished TIA reports as KF QueryResponse (POST /query/tia)</t>
+  </si>
+  <si>
+    <t>Option B of TIA_KF_V2_INTEGRATION.docx; strict models of the documented fields; selector required (no free-text parsing, no analysis started); evidence status carried and weak evidence scored lower; unknowns always included; TIA's own relationship names and directions; redaction per caller.</t>
+  </si>
+  <si>
+    <t>tia/kfadapter.py, docs/KF-ADAPTER.md</t>
+  </si>
+  <si>
+    <t>tests/test_kfadapter.py (14)</t>
+  </si>
+  <si>
+    <t>Built from the document's field list: KF's retriever_api.py was not available, so the models must be re-checked against it.</t>
+  </si>
+  <si>
+    <t>T-050</t>
+  </si>
+  <si>
+    <t>Servlet context paths: a Spring service's own server.servlet.context-path applied to its routes; ones set in a configuration repository reported as an unknown with the setting that applies them</t>
+  </si>
+  <si>
+    <t>Found by the accuracy harness (piggymetrics needed hand configuration).</t>
+  </si>
+  <si>
+    <t>FR-004</t>
+  </si>
+  <si>
+    <t>tia/extract_python.py, tia/impact.py, tia/models.py</t>
+  </si>
+  <si>
+    <t>tests/test_context_paths.py (11)</t>
+  </si>
+  <si>
+    <t>External (config-server) context paths are not applied automatically, only reported.</t>
+  </si>
+  <si>
+    <t>T-051</t>
+  </si>
+  <si>
     <t>GitHub comment upsert (code)</t>
   </si>
   <si>
@@ -1099,7 +1186,7 @@
     <t>marker helper test only</t>
   </si>
   <si>
-    <t>T-048</t>
+    <t>T-052</t>
   </si>
   <si>
     <t>SQLite evidence cache, analysis store, JSONL audit</t>
@@ -1114,7 +1201,7 @@
     <t>test_audit_and_cache</t>
   </si>
   <si>
-    <t>T-049</t>
+    <t>T-053</t>
   </si>
   <si>
     <t>Demo landscape fixture + 29 tests</t>
@@ -1132,7 +1219,7 @@
     <t>29 passed</t>
   </si>
   <si>
-    <t>T-050</t>
+    <t>T-054</t>
   </si>
   <si>
     <t>Separate production code from support code</t>
@@ -1144,7 +1231,7 @@
     <t>tia/, tools/</t>
   </si>
   <si>
-    <t>T-051</t>
+    <t>T-055</t>
   </si>
   <si>
     <t>PR comment + live verification via GitHub App</t>
@@ -1162,25 +1249,7 @@
     <t>GitHub App</t>
   </si>
   <si>
-    <t>T-052</t>
-  </si>
-  <si>
-    <t>Delivery</t>
-  </si>
-  <si>
-    <t>Container images, Docker Compose, Helm chart</t>
-  </si>
-  <si>
-    <t>Images for SaaS and dedicated; documented data locations.</t>
-  </si>
-  <si>
-    <t>PL-009</t>
-  </si>
-  <si>
-    <t>PostgreSQL, queue</t>
-  </si>
-  <si>
-    <t>T-053</t>
+    <t>T-056</t>
   </si>
   <si>
     <t>SaaS production environment (first region)</t>
@@ -1198,7 +1267,7 @@
     <t>Containers</t>
   </si>
   <si>
-    <t>T-054</t>
+    <t>T-057</t>
   </si>
   <si>
     <t>R1 release quality gate</t>
@@ -1210,7 +1279,7 @@
     <t>All R1 tasks</t>
   </si>
   <si>
-    <t>T-055</t>
+    <t>T-058</t>
   </si>
   <si>
     <t>Verification</t>
@@ -1228,7 +1297,7 @@
     <t>P1</t>
   </si>
   <si>
-    <t>T-056</t>
+    <t>T-059</t>
   </si>
   <si>
     <t>Coverage enrichment</t>
@@ -1243,7 +1312,7 @@
     <t>CI results</t>
   </si>
   <si>
-    <t>T-057</t>
+    <t>T-060</t>
   </si>
   <si>
     <t>Regression recommendations + missing-test evidence</t>
@@ -1255,7 +1324,7 @@
     <t>FR-024 FR-025</t>
   </si>
   <si>
-    <t>T-058</t>
+    <t>T-061</t>
   </si>
   <si>
     <t>Contracts</t>
@@ -1267,7 +1336,7 @@
     <t>Enum narrowing, shapes, auth config, configurable compatibility rules.</t>
   </si>
   <si>
-    <t>T-059</t>
+    <t>T-062</t>
   </si>
   <si>
     <t>Event and message contracts (JSON Schema, Avro, Kafka)</t>
@@ -1279,7 +1348,7 @@
     <t>FR-007 FR-019 FR-020 AC-028</t>
   </si>
   <si>
-    <t>T-060</t>
+    <t>T-063</t>
   </si>
   <si>
     <t>Runtime</t>
@@ -1294,7 +1363,7 @@
     <t>FR-026 FR-027 FR-014 AC-007 AC-008</t>
   </si>
   <si>
-    <t>T-061</t>
+    <t>T-064</t>
   </si>
   <si>
     <t>Deployment correlation and environment views</t>
@@ -1306,7 +1375,7 @@
     <t>FR-028 FR-029 AC-029</t>
   </si>
   <si>
-    <t>T-062</t>
+    <t>T-065</t>
   </si>
   <si>
     <t>Governance</t>
@@ -1321,7 +1390,7 @@
     <t>FR-033</t>
   </si>
   <si>
-    <t>T-063</t>
+    <t>T-066</t>
   </si>
   <si>
     <t>Release-policy engine</t>
@@ -1333,7 +1402,7 @@
     <t>FR-033 FR-034 AC-013 AC-014</t>
   </si>
   <si>
-    <t>T-064</t>
+    <t>T-067</t>
   </si>
   <si>
     <t>Advisory and enforcement modes</t>
@@ -1348,10 +1417,7 @@
     <t>Policy engine</t>
   </si>
   <si>
-    <t>T-065</t>
-  </si>
-  <si>
-    <t>Integration</t>
+    <t>T-068</t>
   </si>
   <si>
     <t>GitHub check run</t>
@@ -1360,7 +1426,7 @@
     <t>Policy outcomes in a check run.</t>
   </si>
   <si>
-    <t>T-066</t>
+    <t>T-069</t>
   </si>
   <si>
     <t>ITSM change-record integration (ServiceNow)</t>
@@ -1372,7 +1438,7 @@
     <t>FR-038 AC-031</t>
   </si>
   <si>
-    <t>T-067</t>
+    <t>T-070</t>
   </si>
   <si>
     <t>MCP server and read API for assistants</t>
@@ -1384,7 +1450,7 @@
     <t>FR-037 AC-032</t>
   </si>
   <si>
-    <t>T-068</t>
+    <t>T-071</t>
   </si>
   <si>
     <t>UI</t>
@@ -1402,7 +1468,7 @@
     <t>XL</t>
   </si>
   <si>
-    <t>T-069</t>
+    <t>T-072</t>
   </si>
   <si>
     <t>Administration console</t>
@@ -1417,7 +1483,7 @@
     <t>Web UI</t>
   </si>
   <si>
-    <t>T-070</t>
+    <t>T-073</t>
   </si>
   <si>
     <t>Accessibility WCAG 2.1 AA</t>
@@ -1429,7 +1495,7 @@
     <t>PL-012</t>
   </si>
   <si>
-    <t>T-071</t>
+    <t>T-074</t>
   </si>
   <si>
     <t>SaaS</t>
@@ -1444,7 +1510,7 @@
     <t>PL-014</t>
   </si>
   <si>
-    <t>T-072</t>
+    <t>T-075</t>
   </si>
   <si>
     <t>Data residency (additional regions)</t>
@@ -1456,7 +1522,7 @@
     <t>PL-015 AC-041</t>
   </si>
   <si>
-    <t>T-073</t>
+    <t>T-076</t>
   </si>
   <si>
     <t>Per-tenant keys and BYOK</t>
@@ -1468,7 +1534,7 @@
     <t>PL-016</t>
   </si>
   <si>
-    <t>T-074</t>
+    <t>T-077</t>
   </si>
   <si>
     <t>Dedicated SaaS deployment model</t>
@@ -1480,7 +1546,7 @@
     <t>PL-003</t>
   </si>
   <si>
-    <t>T-075</t>
+    <t>T-078</t>
   </si>
   <si>
     <t>Graph-store benchmark and decision</t>
@@ -1492,7 +1558,7 @@
     <t>12</t>
   </si>
   <si>
-    <t>T-076</t>
+    <t>T-079</t>
   </si>
   <si>
     <t>R2 security review, docs, quality gate</t>
@@ -1501,7 +1567,7 @@
     <t>Per PRD 13/19.</t>
   </si>
   <si>
-    <t>T-077</t>
+    <t>T-080</t>
   </si>
   <si>
     <t>History</t>
@@ -1516,7 +1582,7 @@
     <t>FR-011 FR-030 AC-033</t>
   </si>
   <si>
-    <t>T-078</t>
+    <t>T-081</t>
   </si>
   <si>
     <t>Operations</t>
@@ -1531,7 +1597,7 @@
     <t>FR-031 AC-034</t>
   </si>
   <si>
-    <t>T-079</t>
+    <t>T-082</t>
   </si>
   <si>
     <t>Historical incident investigation</t>
@@ -1543,7 +1609,7 @@
     <t>FR-032 AC-034</t>
   </si>
   <si>
-    <t>T-080</t>
+    <t>T-083</t>
   </si>
   <si>
     <t>Retention enforcement and audit reporting</t>
@@ -1555,7 +1621,7 @@
     <t>11.4</t>
   </si>
   <si>
-    <t>T-081</t>
+    <t>T-084</t>
   </si>
   <si>
     <t>High availability and horizontal scale</t>
@@ -1567,7 +1633,7 @@
     <t>PL-004</t>
   </si>
   <si>
-    <t>T-082</t>
+    <t>T-085</t>
   </si>
   <si>
     <t>Backup, restore, disaster recovery</t>
@@ -1579,7 +1645,7 @@
     <t>PL-005</t>
   </si>
   <si>
-    <t>T-083</t>
+    <t>T-086</t>
   </si>
   <si>
     <t>Customer-hosted and air-gapped installation</t>
@@ -1591,7 +1657,7 @@
     <t>PL-010</t>
   </si>
   <si>
-    <t>T-084</t>
+    <t>T-087</t>
   </si>
   <si>
     <t>SOC 2 Type II / ISO 27001 control set</t>
@@ -1603,7 +1669,7 @@
     <t>PL-018</t>
   </si>
   <si>
-    <t>T-085</t>
+    <t>T-088</t>
   </si>
   <si>
     <t>Public versioned API, OpenAPI spec, client SDK</t>
@@ -1612,13 +1678,13 @@
     <t>Stable external contract.</t>
   </si>
   <si>
-    <t>T-086</t>
+    <t>T-089</t>
   </si>
   <si>
     <t>R3 security review, docs, quality gate</t>
   </si>
   <si>
-    <t>T-087</t>
+    <t>T-090</t>
   </si>
   <si>
     <t>GitLab connector</t>
@@ -1633,7 +1699,7 @@
     <t>P2</t>
   </si>
   <si>
-    <t>T-088</t>
+    <t>T-091</t>
   </si>
   <si>
     <t>Bitbucket connector</t>
@@ -1645,16 +1711,7 @@
     <t>FR-039</t>
   </si>
   <si>
-    <t>T-089</t>
-  </si>
-  <si>
-    <t>Azure DevOps Repos connector</t>
-  </si>
-  <si>
-    <t>PR analysis, comment, status.</t>
-  </si>
-  <si>
-    <t>T-090</t>
+    <t>T-092</t>
   </si>
   <si>
     <t>Adapter SDK</t>
@@ -1666,7 +1723,7 @@
     <t>FR-040</t>
   </si>
   <si>
-    <t>T-091</t>
+    <t>T-093</t>
   </si>
   <si>
     <t>C#/.NET adapter</t>
@@ -1675,7 +1732,7 @@
     <t>ASP.NET Core, HttpClient, EF.</t>
   </si>
   <si>
-    <t>T-092</t>
+    <t>T-094</t>
   </si>
   <si>
     <t>TypeScript/JavaScript adapter</t>
@@ -1684,7 +1741,7 @@
     <t>Express/NestJS, fetch/axios.</t>
   </si>
   <si>
-    <t>T-093</t>
+    <t>T-095</t>
   </si>
   <si>
     <t>Go adapter</t>
@@ -1693,7 +1750,7 @@
     <t>net/http, chi/gin.</t>
   </si>
   <si>
-    <t>T-094</t>
+    <t>T-096</t>
   </si>
   <si>
     <t>Kotlin adapter</t>
@@ -1705,7 +1762,7 @@
     <t>Java adapter</t>
   </si>
   <si>
-    <t>T-095</t>
+    <t>T-097</t>
   </si>
   <si>
     <t>SQL and stored-procedure lineage</t>
@@ -1717,7 +1774,7 @@
     <t>FR-041 AC-037</t>
   </si>
   <si>
-    <t>T-096</t>
+    <t>T-098</t>
   </si>
   <si>
     <t>Event-stream lineage</t>
@@ -1729,7 +1786,7 @@
     <t>FR-042</t>
   </si>
   <si>
-    <t>T-097</t>
+    <t>T-099</t>
   </si>
   <si>
     <t>Analytics</t>
@@ -1744,7 +1801,7 @@
     <t>FR-043</t>
   </si>
   <si>
-    <t>T-098</t>
+    <t>T-100</t>
   </si>
   <si>
     <t>Calibration from validated outcomes</t>
@@ -1756,7 +1813,7 @@
     <t>FR-044 AC-038</t>
   </si>
   <si>
-    <t>T-099</t>
+    <t>T-101</t>
   </si>
   <si>
     <t>Multi-team change coordination</t>
@@ -1768,7 +1825,7 @@
     <t>FR-045</t>
   </si>
   <si>
-    <t>T-100</t>
+    <t>T-102</t>
   </si>
   <si>
     <t>R4 security review, docs, GA quality gate</t>
@@ -1807,7 +1864,7 @@
     <t>GitHub (App and PAT), Azure DevOps (PAT), git URL, local and upload ingestion done; GitHub App verified against a stand-in only; Azure DevOps webhooks/App-equivalent not built</t>
   </si>
   <si>
-    <t>T-017, T-018, T-028, T-041</t>
+    <t>T-017, T-018, T-028, T-041, T-047</t>
   </si>
   <si>
     <t>Revision-aware analysis</t>
@@ -1822,102 +1879,102 @@
     <t>Per-file incremental extraction + persisted versioned graph + full-rescan path with drift repair (Python)</t>
   </si>
   <si>
-    <t>FR-004</t>
-  </si>
-  <si>
     <t>Supported languages (Java + Python)</t>
   </si>
   <si>
     <t>Java (Spring REST, JPA, Flyway/Liquibase) and Python (FastAPI/Flask, SQLAlchemy/Django ORM, Alembic/Django migrations) done; Django REST routes not extracted</t>
   </si>
   <si>
+    <t>T-009, T-029, T-050</t>
+  </si>
+  <si>
+    <t>FR-005</t>
+  </si>
+  <si>
+    <t>Repository freshness</t>
+  </si>
+  <si>
+    <t>Scan status, last successful scan, analysed revision, extractor version (snapshot), failures, stale relationships, inaccessible repos</t>
+  </si>
+  <si>
+    <t>FR-006</t>
+  </si>
+  <si>
+    <t>Core graph entities</t>
+  </si>
+  <si>
+    <t>Service, endpoint, schema, function, call site, test, entity, table, column, migration done; deployment/build/event entities not built</t>
+  </si>
+  <si>
+    <t>FR-006a</t>
+  </si>
+  <si>
+    <t>Data-access scope (ORM/migrations)</t>
+  </si>
+  <si>
+    <t>ORM mappings and migrations extracted; raw SQL/stored procedures (FR-041, R4) reported as data access not fully analysed</t>
+  </si>
+  <si>
+    <t>T-030, T-031</t>
+  </si>
+  <si>
+    <t>FR-007</t>
+  </si>
+  <si>
+    <t>Execution and operations entities</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>FR-008</t>
+  </si>
+  <si>
+    <t>Explicit relationship types</t>
+  </si>
+  <si>
+    <t>FR-009</t>
+  </si>
+  <si>
+    <t>Relationship provenance</t>
+  </si>
+  <si>
+    <t>No last-seen/validity yet (needs persisted graph)</t>
+  </si>
+  <si>
+    <t>FR-010</t>
+  </si>
+  <si>
+    <t>Evidence classifications</t>
+  </si>
+  <si>
+    <t>stale now produced; runtime_observed (R6) never produced yet</t>
+  </si>
+  <si>
+    <t>T-007, T-026</t>
+  </si>
+  <si>
+    <t>FR-011</t>
+  </si>
+  <si>
+    <t>Temporal relationships</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>FR-012</t>
+  </si>
+  <si>
+    <t>Changed-symbol identification</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
     <t>T-009, T-029</t>
   </si>
   <si>
-    <t>FR-005</t>
-  </si>
-  <si>
-    <t>Repository freshness</t>
-  </si>
-  <si>
-    <t>Scan status, last successful scan, analysed revision, extractor version (snapshot), failures, stale relationships, inaccessible repos</t>
-  </si>
-  <si>
-    <t>FR-006</t>
-  </si>
-  <si>
-    <t>Core graph entities</t>
-  </si>
-  <si>
-    <t>Service, endpoint, schema, function, call site, test, entity, table, column, migration done; deployment/build/event entities not built</t>
-  </si>
-  <si>
-    <t>FR-006a</t>
-  </si>
-  <si>
-    <t>Data-access scope (ORM/migrations)</t>
-  </si>
-  <si>
-    <t>ORM mappings and migrations extracted; raw SQL/stored procedures (FR-041, R4) reported as data access not fully analysed</t>
-  </si>
-  <si>
-    <t>T-030, T-031</t>
-  </si>
-  <si>
-    <t>FR-007</t>
-  </si>
-  <si>
-    <t>Execution and operations entities</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>FR-008</t>
-  </si>
-  <si>
-    <t>Explicit relationship types</t>
-  </si>
-  <si>
-    <t>FR-009</t>
-  </si>
-  <si>
-    <t>Relationship provenance</t>
-  </si>
-  <si>
-    <t>No last-seen/validity yet (needs persisted graph)</t>
-  </si>
-  <si>
-    <t>FR-010</t>
-  </si>
-  <si>
-    <t>Evidence classifications</t>
-  </si>
-  <si>
-    <t>stale now produced; runtime_observed (R6) never produced yet</t>
-  </si>
-  <si>
-    <t>T-007, T-026</t>
-  </si>
-  <si>
-    <t>FR-011</t>
-  </si>
-  <si>
-    <t>Temporal relationships</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>FR-012</t>
-  </si>
-  <si>
-    <t>Changed-symbol identification</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
     <t>FR-013</t>
   </si>
   <si>
@@ -1933,7 +1990,7 @@
     <t>R1-R5 done; R6 runtime in R2</t>
   </si>
   <si>
-    <t>T-010, T-060</t>
+    <t>T-010, T-063</t>
   </si>
   <si>
     <t>FR-015</t>
@@ -1972,7 +2029,7 @@
     <t>Basic P0 list done; full comparison R2</t>
   </si>
   <si>
-    <t>T-012, T-058</t>
+    <t>T-012, T-061</t>
   </si>
   <si>
     <t>FR-019</t>
@@ -2065,7 +2122,7 @@
     <t>Configurable policy rules</t>
   </si>
   <si>
-    <t>T-062, T-063</t>
+    <t>T-065, T-066</t>
   </si>
   <si>
     <t>FR-034</t>
@@ -2080,7 +2137,7 @@
     <t>Comment upsert live-verified; publish endpoint and check run built, check run simulated only (needs GitHub App)</t>
   </si>
   <si>
-    <t>T-015, T-034, T-047, T-051, T-065</t>
+    <t>T-015, T-034, T-051, T-055, T-068</t>
   </si>
   <si>
     <t>FR-036</t>
@@ -2104,16 +2161,16 @@
     <t>R4</t>
   </si>
   <si>
-    <t>ADO + generic git URL ingestion done by PAT; PR comment/status and permission mirroring for ADO/GitLab/Bitbucket pending</t>
-  </si>
-  <si>
-    <t>T-087, T-088, T-089</t>
+    <t>Azure DevOps: ingestion, service hooks, PR thread and status (stand-in only); ADO permission mirroring, GitLab and Bitbucket pending</t>
+  </si>
+  <si>
+    <t>T-047, T-090, T-091</t>
   </si>
   <si>
     <t>Adapter SDK + additional languages</t>
   </si>
   <si>
-    <t>T-090, T-091, T-092, T-093, T-094</t>
+    <t>T-092, T-093, T-094, T-095, T-096</t>
   </si>
   <si>
     <t>FR-041</t>
@@ -2152,7 +2209,7 @@
     <t>RLS on every tenant table, tenant resolved from the credential on every request, per-tenant workspace/quota/config/users; webhooks still use the default tenant</t>
   </si>
   <si>
-    <t>T-022, T-074</t>
+    <t>T-022, T-077</t>
   </si>
   <si>
     <t>HA and horizontal scale</t>
@@ -2170,7 +2227,7 @@
     <t>Metrics, JSON logs, traces, health/readiness built; verified against a fake OTLP collector only</t>
   </si>
   <si>
-    <t>T-037, T-053</t>
+    <t>T-037, T-056</t>
   </si>
   <si>
     <t>Versioned public API + SDK</t>
@@ -2179,13 +2236,16 @@
     <t>v1 REST endpoints exist; no OpenAPI publish/SDK</t>
   </si>
   <si>
-    <t>T-016, T-085</t>
+    <t>T-016, T-088</t>
   </si>
   <si>
     <t>Containers, Helm, Compose</t>
   </si>
   <si>
-    <t>T-052, T-053</t>
+    <t>Image, Compose and Helm chart written and statically checked; never built or installed (no Docker here)</t>
+  </si>
+  <si>
+    <t>T-048, T-056</t>
   </si>
   <si>
     <t>Air-gapped install</t>
@@ -2233,7 +2293,7 @@
     <t>Explorer + impact overlay built (v0); filters by severity/evidence/environment, saved views, accessibility, large-scale clustering pending</t>
   </si>
   <si>
-    <t>T-020, T-021, T-068</t>
+    <t>T-020, T-021, T-071</t>
   </si>
   <si>
     <t>Audit</t>
@@ -2242,7 +2302,7 @@
     <t>Tamper-evident keyed chain in PostgreSQL done; GitHub/ADO writes, logins and policy events audited when those features land</t>
   </si>
   <si>
-    <t>T-023, T-048</t>
+    <t>T-023, T-052</t>
   </si>
   <si>
     <t>Data retention</t>
@@ -2395,7 +2455,7 @@
     <t>Comment upsert live on github.com; check run simulated only</t>
   </si>
   <si>
-    <t>T-034, T-051</t>
+    <t>T-034, T-055</t>
   </si>
   <si>
     <t>AC-021</t>
@@ -2449,7 +2509,7 @@
     <t>CI evidence</t>
   </si>
   <si>
-    <t>T-055, T-056</t>
+    <t>T-058, T-059</t>
   </si>
   <si>
     <t>AC-028</t>
@@ -2494,7 +2554,7 @@
     <t>Incident</t>
   </si>
   <si>
-    <t>T-078, T-079</t>
+    <t>T-081, T-082</t>
   </si>
   <si>
     <t>AC-035</t>
@@ -2563,7 +2623,7 @@
     <t>Automatic trigger on PR events (webhook), posting the comment back, check run, Java, ORM/data impact</t>
   </si>
   <si>
-    <t>T-015, T-017, T-018, T-028, T-034, T-041, T-047, T-051, T-065</t>
+    <t>T-015, T-017, T-018, T-028, T-034, T-041, T-047, T-051, T-055, T-068</t>
   </si>
   <si>
     <t>API contract change</t>
@@ -2578,7 +2638,7 @@
     <t>Events and message schemas, full compatibility rules, OpenAPI ingestion, consumer-specific CI test evidence</t>
   </si>
   <si>
-    <t>T-012, T-058, T-059</t>
+    <t>T-012, T-061, T-062</t>
   </si>
   <si>
     <t>Explore the landscape (code graph)</t>
@@ -2602,7 +2662,7 @@
     <t>Incident ingestion, deployment and runtime evidence, historical graph, association labels (never root cause)</t>
   </si>
   <si>
-    <t>T-077, T-078, T-079</t>
+    <t>T-080, T-081, T-082</t>
   </si>
   <si>
     <t>Release-readiness assessment</t>
@@ -2614,7 +2674,7 @@
     <t>CI results, coverage, deployed versions, policy engine, advisory/enforcement mode, ITSM attachment</t>
   </si>
   <si>
-    <t>T-055, T-062, T-063, T-064, T-066</t>
+    <t>T-058, T-065, T-066, T-067, T-069</t>
   </si>
   <si>
     <t>Assistant / MCP retrieval</t>
@@ -2641,7 +2701,7 @@
     <t>R1/R3</t>
   </si>
   <si>
-    <t>T-015, T-023, T-040, T-048, T-080</t>
+    <t>T-015, T-023, T-040, T-052, T-083</t>
   </si>
   <si>
     <t>Use case 1 - Pull-request impact analysis (PRD 5.1): definition of done</t>
@@ -2752,10 +2812,10 @@
     <t>Azure DevOps: service-hook receiver (PR created/updated) with auth verification, PR fetch, repo registration</t>
   </si>
   <si>
-    <t>FR-001 FR-039</t>
-  </si>
-  <si>
-    <t>Ingestion by PAT already works (simulated)</t>
+    <t>tests/test_ado.py: service-hook auth, parsing, routing, dedupe, end-to-end job</t>
+  </si>
+  <si>
+    <t>No real Azure DevOps organisation used</t>
   </si>
   <si>
     <t>UC1-07</t>
@@ -2878,6 +2938,12 @@
     <t>FR-035 FR-039</t>
   </si>
   <si>
+    <t>tests/test_ado.py: one thread updated in place, advisory status, manual publish</t>
+  </si>
+  <si>
+    <t>No real Azure DevOps organisation used; no ADO permission mirroring</t>
+  </si>
+  <si>
     <t>UC1-16</t>
   </si>
   <si>
@@ -2971,7 +3037,13 @@
     <t>Container images, Docker Compose, Helm chart; SaaS environment definition</t>
   </si>
   <si>
-    <t>No Docker/Kubernetes in this environment: build files can be written, not run</t>
+    <t>Built</t>
+  </si>
+  <si>
+    <t>deploy/ + tests/test_deploy.py (static) + a CI job that would build the image</t>
+  </si>
+  <si>
+    <t>Never built, started or installed: no Docker/Kubernetes here</t>
   </si>
   <si>
     <t>UC1-24</t>
@@ -3896,8 +3968,8 @@
         <v>6</v>
       </c>
       <c r="B6" s="6">
-        <f>COUNTA('Task Tracker'!$A$2:$A$251)</f>
-        <v>100</v>
+        <f>COUNTA('Task Tracker'!$A$2:$A$253)</f>
+        <v>102</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>7</v>
@@ -3919,8 +3991,8 @@
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF('Task Tracker'!$I$2:$I$251,"Completed")</f>
-        <v>50</v>
+        <f>COUNTIF('Task Tracker'!$I$2:$I$253,"Completed")</f>
+        <v>54</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>9</v>
@@ -3942,7 +4014,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="6">
-        <f>COUNTIF('Task Tracker'!$I$2:$I$251,"In Progress")</f>
+        <f>COUNTIF('Task Tracker'!$I$2:$I$253,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
@@ -3950,7 +4022,7 @@
       </c>
       <c r="E8" s="6">
         <f>COUNTIF(Requirements!$D$2:$D$120,"Partial")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>11</v>
@@ -3965,15 +4037,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="6">
-        <f>COUNTIF('Task Tracker'!$I$2:$I$251,"Not Started")</f>
-        <v>50</v>
+        <f>COUNTIF('Task Tracker'!$I$2:$I$253,"Not Started")</f>
+        <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="6">
         <f>COUNTIF(Requirements!$D$2:$D$120,"Not started")</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>12</v>
@@ -3988,7 +4060,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="6">
-        <f>COUNTIF('Task Tracker'!$I$2:$I$251,"Blocked")</f>
+        <f>COUNTIF('Task Tracker'!$I$2:$I$253,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -4012,7 +4084,7 @@
       </c>
       <c r="B11" s="7">
         <f>IFERROR(B7/B6,0)</f>
-        <v>0.5</v>
+        <v>0.52941176470588236</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -4020,7 +4092,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="6">
-        <f>SUMPRODUCT(('Task Tracker'!$I$2:$I$251="Completed")*('Task Tracker'!$J$2:$J$251&lt;&gt;1))</f>
+        <f>SUMPRODUCT(('Task Tracker'!$I$2:$I$253="Completed")*('Task Tracker'!$J$2:$J$253&lt;&gt;1))</f>
         <v>0</v>
       </c>
     </row>
@@ -4060,19 +4132,19 @@
         <v>22</v>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIF('Task Tracker'!$B$2:$B$251,$A16)</f>
+        <f>COUNTIF('Task Tracker'!$B$2:$B$253,$A16)</f>
         <v>6</v>
       </c>
       <c r="C16" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A16,'Task Tracker'!$I$2:$I$251,"Completed")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A16,'Task Tracker'!$I$2:$I$253,"Completed")</f>
         <v>6</v>
       </c>
       <c r="D16" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A16,'Task Tracker'!$I$2:$I$251,"In Progress")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A16,'Task Tracker'!$I$2:$I$253,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E16" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A16,'Task Tracker'!$I$2:$I$251,"Not Started")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A16,'Task Tracker'!$I$2:$I$253,"Not Started")</f>
         <v>0</v>
       </c>
       <c r="F16" s="11">
@@ -4091,24 +4163,24 @@
         <v>23</v>
       </c>
       <c r="B17" s="10">
-        <f>COUNTIF('Task Tracker'!$B$2:$B$251,$A17)</f>
+        <f>COUNTIF('Task Tracker'!$B$2:$B$253,$A17)</f>
+        <v>51</v>
+      </c>
+      <c r="C17" s="10">
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A17,'Task Tracker'!$I$2:$I$253,"Completed")</f>
         <v>48</v>
       </c>
-      <c r="C17" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A17,'Task Tracker'!$I$2:$I$251,"Completed")</f>
-        <v>44</v>
-      </c>
       <c r="D17" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A17,'Task Tracker'!$I$2:$I$251,"In Progress")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A17,'Task Tracker'!$I$2:$I$253,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E17" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A17,'Task Tracker'!$I$2:$I$251,"Not Started")</f>
-        <v>4</v>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A17,'Task Tracker'!$I$2:$I$253,"Not Started")</f>
+        <v>3</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>0.91666666666666663</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="G17" s="10">
         <f>COUNTIFS('Acceptance Criteria'!$C$2:$C$72,1,'Acceptance Criteria'!$D$2:$D$72,"Done")</f>
@@ -4124,19 +4196,19 @@
         <v>24</v>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF('Task Tracker'!$B$2:$B$251,$A18)</f>
+        <f>COUNTIF('Task Tracker'!$B$2:$B$253,$A18)</f>
         <v>22</v>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A18,'Task Tracker'!$I$2:$I$251,"Completed")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A18,'Task Tracker'!$I$2:$I$253,"Completed")</f>
         <v>0</v>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A18,'Task Tracker'!$I$2:$I$251,"In Progress")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A18,'Task Tracker'!$I$2:$I$253,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E18" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A18,'Task Tracker'!$I$2:$I$251,"Not Started")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A18,'Task Tracker'!$I$2:$I$253,"Not Started")</f>
         <v>22</v>
       </c>
       <c r="F18" s="11">
@@ -4157,19 +4229,19 @@
         <v>25</v>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF('Task Tracker'!$B$2:$B$251,$A19)</f>
+        <f>COUNTIF('Task Tracker'!$B$2:$B$253,$A19)</f>
         <v>10</v>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A19,'Task Tracker'!$I$2:$I$251,"Completed")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A19,'Task Tracker'!$I$2:$I$253,"Completed")</f>
         <v>0</v>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A19,'Task Tracker'!$I$2:$I$251,"In Progress")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A19,'Task Tracker'!$I$2:$I$253,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E19" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A19,'Task Tracker'!$I$2:$I$251,"Not Started")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A19,'Task Tracker'!$I$2:$I$253,"Not Started")</f>
         <v>10</v>
       </c>
       <c r="F19" s="11">
@@ -4190,20 +4262,20 @@
         <v>26</v>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF('Task Tracker'!$B$2:$B$251,$A20)</f>
-        <v>14</v>
+        <f>COUNTIF('Task Tracker'!$B$2:$B$253,$A20)</f>
+        <v>13</v>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A20,'Task Tracker'!$I$2:$I$251,"Completed")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A20,'Task Tracker'!$I$2:$I$253,"Completed")</f>
         <v>0</v>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A20,'Task Tracker'!$I$2:$I$251,"In Progress")</f>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A20,'Task Tracker'!$I$2:$I$253,"In Progress")</f>
         <v>0</v>
       </c>
       <c r="E20" s="10">
-        <f>COUNTIFS('Task Tracker'!$B$2:$B$251,$A20,'Task Tracker'!$I$2:$I$251,"Not Started")</f>
-        <v>14</v>
+        <f>COUNTIFS('Task Tracker'!$B$2:$B$253,$A20,'Task Tracker'!$I$2:$I$253,"Not Started")</f>
+        <v>13</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
@@ -4224,11 +4296,11 @@
       </c>
       <c r="B21" s="13">
         <f>SUM(B16:B20)</f>
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C21" s="13">
         <f>SUM(C16:C20)</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D21" s="13">
         <f>SUM(D16:D20)</f>
@@ -4236,11 +4308,11 @@
       </c>
       <c r="E21" s="13">
         <f>SUM(E16:E20)</f>
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="G21" s="13">
         <f>SUM(G16:G20)</f>
@@ -4267,7 +4339,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -6420,7 +6492,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" ht="75" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
         <v>345</v>
       </c>
@@ -6428,7 +6500,7 @@
         <v>23</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D48" s="16" t="s">
         <v>346</v>
@@ -6462,29 +6534,31 @@
       <c r="O48" s="16" t="s">
         <v>350</v>
       </c>
-      <c r="P48" s="16"/>
-    </row>
-    <row r="49" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+      <c r="P48" s="16" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="50" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>172</v>
+        <v>353</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>183</v>
+        <v>356</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H49" s="15" t="s">
         <v>49</v>
@@ -6504,31 +6578,33 @@
         <v>46323</v>
       </c>
       <c r="O49" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="P49" s="16"/>
-    </row>
-    <row r="50" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+      <c r="P49" s="16" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="75" x14ac:dyDescent="0.35">
       <c r="A50" s="15" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>359</v>
+        <v>47</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H50" s="15" t="s">
         <v>49</v>
@@ -6548,31 +6624,33 @@
         <v>46323</v>
       </c>
       <c r="O50" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="P50" s="16"/>
-    </row>
-    <row r="51" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+        <v>365</v>
+      </c>
+      <c r="P50" s="16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="50" x14ac:dyDescent="0.35">
       <c r="A51" s="15" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B51" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>311</v>
+        <v>85</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>47</v>
+        <v>370</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H51" s="15" t="s">
         <v>49</v>
@@ -6592,321 +6670,339 @@
         <v>46323</v>
       </c>
       <c r="O51" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="P51" s="16"/>
+        <v>372</v>
+      </c>
+      <c r="P51" s="16" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A52" s="15" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B52" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="G52" s="16"/>
+        <v>377</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>378</v>
+      </c>
       <c r="H52" s="15" t="s">
         <v>49</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="J52" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="L52" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="M52" s="17">
-        <v>1</v>
-      </c>
-      <c r="N52" s="19"/>
-      <c r="O52" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="L52" s="16"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="19">
+        <v>46323</v>
+      </c>
+      <c r="O52" s="16" t="s">
+        <v>379</v>
+      </c>
       <c r="P52" s="16"/>
     </row>
     <row r="53" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A53" s="15" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>373</v>
+        <v>172</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="G53" s="16"/>
+        <v>183</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>383</v>
+      </c>
       <c r="H53" s="15" t="s">
         <v>49</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="J53" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L53" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="M53" s="17">
-        <v>2</v>
-      </c>
-      <c r="N53" s="19"/>
-      <c r="O53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="19">
+        <v>46323</v>
+      </c>
+      <c r="O53" s="16" t="s">
+        <v>384</v>
+      </c>
       <c r="P53" s="16"/>
     </row>
-    <row r="54" spans="1:16" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A54" s="15" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B54" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>381</v>
-      </c>
-      <c r="G54" s="16"/>
+        <v>388</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>389</v>
+      </c>
       <c r="H54" s="15" t="s">
         <v>49</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="J54" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="L54" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="M54" s="17">
-        <v>3</v>
-      </c>
-      <c r="N54" s="19"/>
-      <c r="O54" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="L54" s="16"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="19">
+        <v>46323</v>
+      </c>
+      <c r="O54" s="16" t="s">
+        <v>390</v>
+      </c>
       <c r="P54" s="16"/>
     </row>
     <row r="55" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A55" s="15" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B55" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>18</v>
+        <v>311</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="G55" s="16"/>
+        <v>47</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>394</v>
+      </c>
       <c r="H55" s="15" t="s">
         <v>49</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
       <c r="J55" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="L55" s="16" t="s">
-        <v>387</v>
-      </c>
-      <c r="M55" s="17">
-        <v>4</v>
-      </c>
-      <c r="N55" s="19"/>
-      <c r="O55" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="L55" s="16"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="19">
+        <v>46323</v>
+      </c>
+      <c r="O55" s="16" t="s">
+        <v>390</v>
+      </c>
       <c r="P55" s="16"/>
     </row>
     <row r="56" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A56" s="15" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>389</v>
+        <v>137</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>392</v>
+        <v>259</v>
       </c>
       <c r="G56" s="16"/>
       <c r="H56" s="15" t="s">
-        <v>393</v>
+        <v>49</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J56" s="18">
         <v>0</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="L56" s="16"/>
-      <c r="M56" s="17"/>
+        <v>399</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="M56" s="17">
+        <v>1</v>
+      </c>
       <c r="N56" s="19"/>
       <c r="O56" s="16"/>
       <c r="P56" s="16"/>
     </row>
-    <row r="57" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A57" s="15" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G57" s="16"/>
       <c r="H57" s="15" t="s">
-        <v>393</v>
+        <v>49</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J57" s="18">
         <v>0</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>50</v>
+        <v>405</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="M57" s="17"/>
+        <v>406</v>
+      </c>
+      <c r="M57" s="17">
+        <v>2</v>
+      </c>
       <c r="N57" s="19"/>
       <c r="O57" s="16"/>
       <c r="P57" s="16"/>
     </row>
     <row r="58" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A58" s="15" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>389</v>
+        <v>18</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>402</v>
+        <v>334</v>
       </c>
       <c r="G58" s="16"/>
       <c r="H58" s="15" t="s">
-        <v>393</v>
+        <v>49</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J58" s="18">
         <v>0</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>50</v>
+        <v>399</v>
       </c>
       <c r="L58" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="M58" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="M58" s="17">
+        <v>3</v>
+      </c>
       <c r="N58" s="19"/>
       <c r="O58" s="16"/>
       <c r="P58" s="16"/>
     </row>
     <row r="59" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A59" s="15" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B59" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>107</v>
+        <v>415</v>
       </c>
       <c r="G59" s="16"/>
       <c r="H59" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J59" s="18">
         <v>0</v>
@@ -6922,37 +7018,39 @@
     </row>
     <row r="60" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A60" s="15" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="B60" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G60" s="16"/>
       <c r="H60" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J60" s="18">
         <v>0</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="L60" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>421</v>
+      </c>
       <c r="M60" s="17"/>
       <c r="N60" s="19"/>
       <c r="O60" s="16"/>
@@ -6960,7 +7058,7 @@
     </row>
     <row r="61" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A61" s="15" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B61" s="16" t="s">
         <v>24</v>
@@ -6969,28 +7067,30 @@
         <v>412</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="G61" s="16"/>
       <c r="H61" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J61" s="18">
         <v>0</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="L61" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>421</v>
+      </c>
       <c r="M61" s="17"/>
       <c r="N61" s="19"/>
       <c r="O61" s="16"/>
@@ -6998,35 +7098,35 @@
     </row>
     <row r="62" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A62" s="15" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="G62" s="16"/>
       <c r="H62" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J62" s="18">
         <v>0</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>382</v>
+        <v>50</v>
       </c>
       <c r="L62" s="16"/>
       <c r="M62" s="17"/>
@@ -7036,35 +7136,35 @@
     </row>
     <row r="63" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G63" s="16"/>
       <c r="H63" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J63" s="18">
         <v>0</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>50</v>
+        <v>405</v>
       </c>
       <c r="L63" s="16"/>
       <c r="M63" s="17"/>
@@ -7074,35 +7174,35 @@
     </row>
     <row r="64" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A64" s="15" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G64" s="16"/>
       <c r="H64" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J64" s="18">
         <v>0</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="L64" s="16"/>
       <c r="M64" s="17"/>
@@ -7112,39 +7212,37 @@
     </row>
     <row r="65" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A65" s="15" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="G65" s="16"/>
       <c r="H65" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J65" s="18">
         <v>0</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="L65" s="16" t="s">
-        <v>433</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="L65" s="16"/>
       <c r="M65" s="17"/>
       <c r="N65" s="19"/>
       <c r="O65" s="16"/>
@@ -7152,29 +7250,29 @@
     </row>
     <row r="66" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A66" s="15" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B66" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>348</v>
+        <v>447</v>
       </c>
       <c r="G66" s="16"/>
       <c r="H66" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J66" s="18">
         <v>0</v>
@@ -7182,9 +7280,7 @@
       <c r="K66" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L66" s="16" t="s">
-        <v>433</v>
-      </c>
+      <c r="L66" s="16"/>
       <c r="M66" s="17"/>
       <c r="N66" s="19"/>
       <c r="O66" s="16"/>
@@ -7192,35 +7288,35 @@
     </row>
     <row r="67" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A67" s="15" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B67" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="G67" s="16"/>
       <c r="H67" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J67" s="18">
         <v>0</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="L67" s="16"/>
       <c r="M67" s="17"/>
@@ -7230,29 +7326,29 @@
     </row>
     <row r="68" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A68" s="15" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B68" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="G68" s="16"/>
       <c r="H68" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J68" s="18">
         <v>0</v>
@@ -7260,45 +7356,49 @@
       <c r="K68" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L68" s="16"/>
+      <c r="L68" s="16" t="s">
+        <v>456</v>
+      </c>
       <c r="M68" s="17"/>
       <c r="N68" s="19"/>
       <c r="O68" s="16"/>
       <c r="P68" s="16"/>
     </row>
-    <row r="69" spans="1:16" ht="50" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A69" s="15" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B69" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>447</v>
+        <v>361</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>450</v>
+        <v>377</v>
       </c>
       <c r="G69" s="16"/>
       <c r="H69" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J69" s="18">
         <v>0</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="L69" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>456</v>
+      </c>
       <c r="M69" s="17"/>
       <c r="N69" s="19"/>
       <c r="O69" s="16"/>
@@ -7306,39 +7406,37 @@
     </row>
     <row r="70" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A70" s="15" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B70" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>447</v>
+        <v>361</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="G70" s="16"/>
       <c r="H70" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J70" s="18">
         <v>0</v>
       </c>
       <c r="K70" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="L70" s="16" t="s">
-        <v>456</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="L70" s="16"/>
       <c r="M70" s="17"/>
       <c r="N70" s="19"/>
       <c r="O70" s="16"/>
@@ -7346,29 +7444,29 @@
     </row>
     <row r="71" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A71" s="15" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B71" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>447</v>
+        <v>361</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="G71" s="16"/>
       <c r="H71" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J71" s="18">
         <v>0</v>
@@ -7376,45 +7474,43 @@
       <c r="K71" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L71" s="16" t="s">
-        <v>456</v>
-      </c>
+      <c r="L71" s="16"/>
       <c r="M71" s="17"/>
       <c r="N71" s="19"/>
       <c r="O71" s="16"/>
       <c r="P71" s="16"/>
     </row>
-    <row r="72" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" ht="50" x14ac:dyDescent="0.35">
       <c r="A72" s="15" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="B72" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="G72" s="16"/>
       <c r="H72" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J72" s="18">
         <v>0</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>50</v>
+        <v>473</v>
       </c>
       <c r="L72" s="16"/>
       <c r="M72" s="17"/>
@@ -7424,37 +7520,39 @@
     </row>
     <row r="73" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A73" s="15" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B73" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="G73" s="16"/>
       <c r="H73" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J73" s="18">
         <v>0</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="L73" s="16"/>
+        <v>405</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>478</v>
+      </c>
       <c r="M73" s="17"/>
       <c r="N73" s="19"/>
       <c r="O73" s="16"/>
@@ -7462,29 +7560,29 @@
     </row>
     <row r="74" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A74" s="15" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B74" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="G74" s="16"/>
       <c r="H74" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J74" s="18">
         <v>0</v>
@@ -7492,7 +7590,9 @@
       <c r="K74" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L74" s="16"/>
+      <c r="L74" s="16" t="s">
+        <v>478</v>
+      </c>
       <c r="M74" s="17"/>
       <c r="N74" s="19"/>
       <c r="O74" s="16"/>
@@ -7500,29 +7600,29 @@
     </row>
     <row r="75" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A75" s="15" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="B75" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G75" s="16"/>
       <c r="H75" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J75" s="18">
         <v>0</v>
@@ -7538,35 +7638,35 @@
     </row>
     <row r="76" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A76" s="15" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B76" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>172</v>
+        <v>484</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="G76" s="16"/>
       <c r="H76" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J76" s="18">
         <v>0</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>50</v>
+        <v>405</v>
       </c>
       <c r="L76" s="16"/>
       <c r="M76" s="17"/>
@@ -7576,29 +7676,29 @@
     </row>
     <row r="77" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A77" s="15" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="B77" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>18</v>
+        <v>484</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>334</v>
+        <v>495</v>
       </c>
       <c r="G77" s="16"/>
       <c r="H77" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J77" s="18">
         <v>0</v>
@@ -7614,35 +7714,35 @@
     </row>
     <row r="78" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A78" s="15" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="G78" s="16"/>
       <c r="H78" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J78" s="18">
         <v>0</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>382</v>
+        <v>50</v>
       </c>
       <c r="L78" s="16"/>
       <c r="M78" s="17"/>
@@ -7652,35 +7752,35 @@
     </row>
     <row r="79" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A79" s="15" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>491</v>
+        <v>172</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="G79" s="16"/>
       <c r="H79" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J79" s="18">
         <v>0</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>382</v>
+        <v>50</v>
       </c>
       <c r="L79" s="16"/>
       <c r="M79" s="17"/>
@@ -7690,29 +7790,29 @@
     </row>
     <row r="80" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A80" s="15" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>491</v>
+        <v>18</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>498</v>
+        <v>334</v>
       </c>
       <c r="G80" s="16"/>
       <c r="H80" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J80" s="18">
         <v>0</v>
@@ -7728,35 +7828,35 @@
     </row>
     <row r="81" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A81" s="15" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B81" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>421</v>
+        <v>508</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="G81" s="16"/>
       <c r="H81" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J81" s="18">
         <v>0</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>50</v>
+        <v>405</v>
       </c>
       <c r="L81" s="16"/>
       <c r="M81" s="17"/>
@@ -7766,35 +7866,35 @@
     </row>
     <row r="82" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A82" s="15" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B82" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>172</v>
+        <v>513</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="G82" s="16"/>
       <c r="H82" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J82" s="18">
         <v>0</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="L82" s="16"/>
       <c r="M82" s="17"/>
@@ -7804,29 +7904,29 @@
     </row>
     <row r="83" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A83" s="15" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="B83" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>172</v>
+        <v>513</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G83" s="16"/>
       <c r="H83" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J83" s="18">
         <v>0</v>
@@ -7842,29 +7942,29 @@
     </row>
     <row r="84" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A84" s="15" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="B84" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>373</v>
+        <v>444</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="G84" s="16"/>
       <c r="H84" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J84" s="18">
         <v>0</v>
@@ -7880,35 +7980,35 @@
     </row>
     <row r="85" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A85" s="15" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="B85" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>462</v>
+        <v>172</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="G85" s="16"/>
       <c r="H85" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J85" s="18">
         <v>0</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="L85" s="16"/>
       <c r="M85" s="17"/>
@@ -7918,7 +8018,7 @@
     </row>
     <row r="86" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A86" s="15" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B86" s="16" t="s">
         <v>25</v>
@@ -7927,20 +8027,20 @@
         <v>172</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>133</v>
+        <v>532</v>
       </c>
       <c r="G86" s="16"/>
       <c r="H86" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J86" s="18">
         <v>0</v>
@@ -7956,29 +8056,29 @@
     </row>
     <row r="87" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A87" s="15" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="B87" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>18</v>
+        <v>353</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>334</v>
+        <v>536</v>
       </c>
       <c r="G87" s="16"/>
       <c r="H87" s="15" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J87" s="18">
         <v>0</v>
@@ -7994,35 +8094,35 @@
     </row>
     <row r="88" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A88" s="15" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>137</v>
+        <v>484</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="G88" s="16"/>
       <c r="H88" s="15" t="s">
-        <v>528</v>
+        <v>416</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J88" s="18">
         <v>0</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="L88" s="16"/>
       <c r="M88" s="17"/>
@@ -8032,35 +8132,35 @@
     </row>
     <row r="89" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A89" s="15" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>532</v>
+        <v>133</v>
       </c>
       <c r="G89" s="16"/>
       <c r="H89" s="15" t="s">
-        <v>528</v>
+        <v>416</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J89" s="18">
         <v>0</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>382</v>
+        <v>50</v>
       </c>
       <c r="L89" s="16"/>
       <c r="M89" s="17"/>
@@ -8070,35 +8170,35 @@
     </row>
     <row r="90" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A90" s="15" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>532</v>
+        <v>334</v>
       </c>
       <c r="G90" s="16"/>
       <c r="H90" s="15" t="s">
-        <v>528</v>
+        <v>416</v>
       </c>
       <c r="I90" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J90" s="18">
         <v>0</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>382</v>
+        <v>50</v>
       </c>
       <c r="L90" s="16"/>
       <c r="M90" s="17"/>
@@ -8108,35 +8208,35 @@
     </row>
     <row r="91" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A91" s="15" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="B91" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="G91" s="16"/>
       <c r="H91" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J91" s="18">
         <v>0</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>50</v>
+        <v>405</v>
       </c>
       <c r="L91" s="16"/>
       <c r="M91" s="17"/>
@@ -8146,35 +8246,35 @@
     </row>
     <row r="92" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A92" s="15" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B92" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="G92" s="16"/>
       <c r="H92" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J92" s="18">
         <v>0</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="L92" s="16"/>
       <c r="M92" s="17"/>
@@ -8184,7 +8284,7 @@
     </row>
     <row r="93" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A93" s="15" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B93" s="16" t="s">
         <v>26</v>
@@ -8193,26 +8293,26 @@
         <v>85</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="G93" s="16"/>
       <c r="H93" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J93" s="18">
         <v>0</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>451</v>
+        <v>50</v>
       </c>
       <c r="L93" s="16"/>
       <c r="M93" s="17"/>
@@ -8222,7 +8322,7 @@
     </row>
     <row r="94" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A94" s="15" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="B94" s="16" t="s">
         <v>26</v>
@@ -8231,26 +8331,26 @@
         <v>85</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="G94" s="16"/>
       <c r="H94" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J94" s="18">
         <v>0</v>
       </c>
       <c r="K94" s="15" t="s">
-        <v>382</v>
+        <v>473</v>
       </c>
       <c r="L94" s="16"/>
       <c r="M94" s="17"/>
@@ -8260,7 +8360,7 @@
     </row>
     <row r="95" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A95" s="15" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B95" s="16" t="s">
         <v>26</v>
@@ -8269,30 +8369,28 @@
         <v>85</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="G95" s="16"/>
       <c r="H95" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J95" s="18">
         <v>0</v>
       </c>
       <c r="K95" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="L95" s="16" t="s">
-        <v>552</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="L95" s="16"/>
       <c r="M95" s="17"/>
       <c r="N95" s="19"/>
       <c r="O95" s="16"/>
@@ -8300,7 +8398,7 @@
     </row>
     <row r="96" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A96" s="15" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="B96" s="16" t="s">
         <v>26</v>
@@ -8309,26 +8407,26 @@
         <v>85</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G96" s="16"/>
       <c r="H96" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I96" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J96" s="18">
         <v>0</v>
       </c>
       <c r="K96" s="15" t="s">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="L96" s="16"/>
       <c r="M96" s="17"/>
@@ -8338,7 +8436,7 @@
     </row>
     <row r="97" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A97" s="15" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B97" s="16" t="s">
         <v>26</v>
@@ -8347,28 +8445,30 @@
         <v>85</v>
       </c>
       <c r="D97" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="F97" s="16" t="s">
         <v>558</v>
-      </c>
-      <c r="E97" s="16" t="s">
-        <v>559</v>
-      </c>
-      <c r="F97" s="16" t="s">
-        <v>560</v>
       </c>
       <c r="G97" s="16"/>
       <c r="H97" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J97" s="18">
         <v>0</v>
       </c>
       <c r="K97" s="15" t="s">
-        <v>382</v>
-      </c>
-      <c r="L97" s="16"/>
+        <v>405</v>
+      </c>
+      <c r="L97" s="16" t="s">
+        <v>571</v>
+      </c>
       <c r="M97" s="17"/>
       <c r="N97" s="19"/>
       <c r="O97" s="16"/>
@@ -8376,35 +8476,35 @@
     </row>
     <row r="98" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A98" s="15" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="B98" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>562</v>
+        <v>85</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="G98" s="16"/>
       <c r="H98" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J98" s="18">
         <v>0</v>
       </c>
       <c r="K98" s="15" t="s">
-        <v>50</v>
+        <v>473</v>
       </c>
       <c r="L98" s="16"/>
       <c r="M98" s="17"/>
@@ -8414,35 +8514,35 @@
     </row>
     <row r="99" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A99" s="15" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="B99" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>562</v>
+        <v>85</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="G99" s="16"/>
       <c r="H99" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J99" s="18">
         <v>0</v>
       </c>
       <c r="K99" s="15" t="s">
-        <v>50</v>
+        <v>405</v>
       </c>
       <c r="L99" s="16"/>
       <c r="M99" s="17"/>
@@ -8452,29 +8552,29 @@
     </row>
     <row r="100" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A100" s="15" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="B100" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>435</v>
+        <v>581</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="G100" s="16"/>
       <c r="H100" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J100" s="18">
         <v>0</v>
@@ -8490,29 +8590,29 @@
     </row>
     <row r="101" spans="1:16" ht="25" x14ac:dyDescent="0.35">
       <c r="A101" s="15" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="B101" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>18</v>
+        <v>581</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>484</v>
+        <v>587</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>334</v>
+        <v>588</v>
       </c>
       <c r="G101" s="16"/>
       <c r="H101" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="J101" s="18">
         <v>0</v>
@@ -8526,9 +8626,85 @@
       <c r="O101" s="16"/>
       <c r="P101" s="16"/>
     </row>
+    <row r="102" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+      <c r="A102" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="E102" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="F102" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="G102" s="16"/>
+      <c r="H102" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="I102" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="J102" s="18">
+        <v>0</v>
+      </c>
+      <c r="K102" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L102" s="16"/>
+      <c r="M102" s="17"/>
+      <c r="N102" s="19"/>
+      <c r="O102" s="16"/>
+      <c r="P102" s="16"/>
+    </row>
+    <row r="103" spans="1:16" ht="25" x14ac:dyDescent="0.35">
+      <c r="A103" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="E103" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="G103" s="16"/>
+      <c r="H103" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="I103" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="J103" s="18">
+        <v>0</v>
+      </c>
+      <c r="K103" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L103" s="16"/>
+      <c r="M103" s="17"/>
+      <c r="N103" s="19"/>
+      <c r="O103" s="16"/>
+      <c r="P103" s="16"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P101" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="I2:I251">
+  <autoFilter ref="A1:P103" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="I2:I253">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
@@ -8543,13 +8719,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="I2:I251" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="I2:I253" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Completed,In Progress,Not Started,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H251" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="H2:H253" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" sqref="J2:J251" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="decimal" sqref="J2:J253" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -8576,17 +8752,17 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>576</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>578</v>
+        <v>597</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
@@ -8601,7 +8777,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>38</v>
@@ -8618,35 +8794,35 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>T-051</v>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>T-055</v>
       </c>
       <c r="C5" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>PR comment + live verification via GitHub App</v>
       </c>
       <c r="D5" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>R1 Platform foundation &amp; cross-repo impact</v>
       </c>
       <c r="E5" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>FR-035 AC-020</v>
       </c>
       <c r="F5" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>S</v>
       </c>
       <c r="G5" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>GitHub App</v>
       </c>
       <c r="H5" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>Not Started</v>
       </c>
       <c r="I5" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A5,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A5,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>Update in place on push; never blocks merge.</v>
       </c>
     </row>
@@ -8655,36 +8831,36 @@
         <v>2</v>
       </c>
       <c r="B6" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>T-052</v>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>T-056</v>
       </c>
       <c r="C6" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>Container images, Docker Compose, Helm chart</v>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>SaaS production environment (first region)</v>
       </c>
       <c r="D6" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>R1 Platform foundation &amp; cross-repo impact</v>
       </c>
       <c r="E6" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>PL-009</v>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>PL-009 PL-007</v>
       </c>
       <c r="F6" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>M</v>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>L</v>
       </c>
       <c r="G6" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>PostgreSQL, queue</v>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>Containers</v>
       </c>
       <c r="H6" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>Not Started</v>
       </c>
       <c r="I6" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A6,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>Images for SaaS and dedicated; documented data locations.</v>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A6,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>Infrastructure as code, gateway with tenant resolution and rate limits, managed PostgreSQL, evidence store, secrets, monitoring.</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -8692,36 +8868,36 @@
         <v>3</v>
       </c>
       <c r="B7" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>T-053</v>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>T-057</v>
       </c>
       <c r="C7" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>SaaS production environment (first region)</v>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>R1 release quality gate</v>
       </c>
       <c r="D7" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>R1 Platform foundation &amp; cross-repo impact</v>
       </c>
       <c r="E7" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>PL-009 PL-007</v>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>PRD-19</v>
       </c>
       <c r="F7" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>L</v>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>S</v>
       </c>
       <c r="G7" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>Containers</v>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>All R1 tasks</v>
       </c>
       <c r="H7" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v>Not Started</v>
       </c>
       <c r="I7" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A7,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>Infrastructure as code, gateway with tenant resolution and rate limits, managed PostgreSQL, evidence store, secrets, monitoring.</v>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A7,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v>All R1 ACs, accuracy, performance, security, operability, docs.</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -8729,36 +8905,36 @@
         <v>4</v>
       </c>
       <c r="B8" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>T-054</v>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
       <c r="C8" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>R1 release quality gate</v>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
       <c r="D8" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>R1 Platform foundation &amp; cross-repo impact</v>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
       <c r="E8" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>PRD-19</v>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
       <c r="F8" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>S</v>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
       <c r="G8" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>All R1 tasks</v>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
       <c r="H8" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>Not Started</v>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
       <c r="I8" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A8,'Task Tracker'!$M$2:$M$251,0)),"")</f>
-        <v>All R1 ACs, accuracy, performance, security, operability, docs.</v>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A8,'Task Tracker'!$M$2:$M$253,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -8766,35 +8942,35 @@
         <v>5</v>
       </c>
       <c r="B9" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C9" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F9" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G9" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H9" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A9,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A9,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -8803,35 +8979,35 @@
         <v>6</v>
       </c>
       <c r="B10" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C10" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F10" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G10" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H10" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I10" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A10,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A10,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -8840,35 +9016,35 @@
         <v>7</v>
       </c>
       <c r="B11" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C11" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F11" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G11" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H11" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A11,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A11,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -8877,35 +9053,35 @@
         <v>8</v>
       </c>
       <c r="B12" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C12" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F12" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G12" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H12" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I12" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A12,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A12,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -8914,35 +9090,35 @@
         <v>9</v>
       </c>
       <c r="B13" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C13" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F13" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G13" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H13" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A13,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A13,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -8951,35 +9127,35 @@
         <v>10</v>
       </c>
       <c r="B14" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C14" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F14" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G14" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H14" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A14,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A14,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -8988,35 +9164,35 @@
         <v>11</v>
       </c>
       <c r="B15" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C15" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F15" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G15" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H15" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A15,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A15,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9025,35 +9201,35 @@
         <v>12</v>
       </c>
       <c r="B16" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C16" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F16" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G16" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H16" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A16,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A16,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9062,35 +9238,35 @@
         <v>13</v>
       </c>
       <c r="B17" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C17" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G17" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H17" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A17,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A17,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9099,35 +9275,35 @@
         <v>14</v>
       </c>
       <c r="B18" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C18" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F18" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G18" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H18" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A18,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A18,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9136,35 +9312,35 @@
         <v>15</v>
       </c>
       <c r="B19" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C19" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F19" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G19" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H19" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I19" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A19,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A19,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9173,35 +9349,35 @@
         <v>16</v>
       </c>
       <c r="B20" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C20" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F20" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G20" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H20" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I20" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A20,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A20,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9210,35 +9386,35 @@
         <v>17</v>
       </c>
       <c r="B21" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C21" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G21" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H21" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A21,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A21,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9247,35 +9423,35 @@
         <v>18</v>
       </c>
       <c r="B22" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C22" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F22" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G22" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H22" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I22" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A22,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A22,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9284,35 +9460,35 @@
         <v>19</v>
       </c>
       <c r="B23" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C23" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F23" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G23" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H23" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A23,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A23,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9321,35 +9497,35 @@
         <v>20</v>
       </c>
       <c r="B24" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C24" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F24" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G24" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H24" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A24,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A24,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9358,35 +9534,35 @@
         <v>21</v>
       </c>
       <c r="B25" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G25" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H25" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A25,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A25,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9395,35 +9571,35 @@
         <v>22</v>
       </c>
       <c r="B26" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C26" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G26" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H26" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A26,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A26,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9432,35 +9608,35 @@
         <v>23</v>
       </c>
       <c r="B27" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C27" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F27" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G27" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H27" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A27,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A27,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9469,35 +9645,35 @@
         <v>24</v>
       </c>
       <c r="B28" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C28" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F28" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G28" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H28" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I28" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A28,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A28,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9506,35 +9682,35 @@
         <v>25</v>
       </c>
       <c r="B29" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C29" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F29" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G29" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H29" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I29" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A29,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A29,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9543,35 +9719,35 @@
         <v>26</v>
       </c>
       <c r="B30" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C30" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F30" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G30" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H30" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I30" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A30,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A30,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9580,35 +9756,35 @@
         <v>27</v>
       </c>
       <c r="B31" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C31" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F31" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G31" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H31" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I31" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A31,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A31,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9617,35 +9793,35 @@
         <v>28</v>
       </c>
       <c r="B32" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C32" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F32" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G32" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H32" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I32" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A32,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A32,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9654,35 +9830,35 @@
         <v>29</v>
       </c>
       <c r="B33" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C33" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F33" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G33" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H33" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I33" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A33,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A33,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9691,35 +9867,35 @@
         <v>30</v>
       </c>
       <c r="B34" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$A$2:$A$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$D$2:$D$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$B$2:$B$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$F$2:$F$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$K$2:$K$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$L$2:$L$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="H34" s="15" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$I$2:$I$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
       <c r="I34" s="16" t="str">
-        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$251,MATCH($A34,'Task Tracker'!$M$2:$M$251,0)),"")</f>
+        <f>IFERROR(INDEX('Task Tracker'!$E$2:$E$253,MATCH($A34,'Task Tracker'!$M$2:$M$253,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -9743,10 +9919,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>580</v>
+        <v>599</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>18</v>
@@ -9755,10 +9931,10 @@
         <v>35</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
@@ -9766,19 +9942,19 @@
         <v>147</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -9786,10 +9962,10 @@
         <v>80</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>9</v>
@@ -9801,19 +9977,19 @@
     </row>
     <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>194</v>
@@ -9821,39 +9997,39 @@
     </row>
     <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>592</v>
+        <v>370</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>593</v>
+        <v>611</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>201</v>
@@ -9861,19 +10037,19 @@
     </row>
     <row r="7" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>228</v>
@@ -9881,51 +10057,51 @@
     </row>
     <row r="8" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>605</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>9</v>
@@ -9937,96 +10113,96 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
-        <v>611</v>
+        <v>629</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>614</v>
+        <v>632</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>615</v>
+        <v>633</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>617</v>
+        <v>635</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="16" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>595</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>625</v>
+        <v>644</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="16" t="s">
-        <v>626</v>
+        <v>645</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -10034,50 +10210,50 @@
         <v>95</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>627</v>
+        <v>646</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>628</v>
+        <v>647</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>629</v>
+        <v>648</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>630</v>
+        <v>649</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>631</v>
+        <v>650</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>632</v>
+        <v>651</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>633</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>634</v>
+        <v>653</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>9</v>
@@ -10089,22 +10265,22 @@
     </row>
     <row r="19" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>637</v>
+        <v>656</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>638</v>
+        <v>657</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>595</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -10112,74 +10288,74 @@
         <v>107</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>642</v>
+        <v>661</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>644</v>
+        <v>663</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>645</v>
+        <v>664</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>647</v>
+        <v>666</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
-        <v>648</v>
+        <v>667</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="F23" s="16" t="s">
         <v>98</v>
@@ -10187,457 +10363,457 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="16"/>
       <c r="F24" s="16" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D25" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="16" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>654</v>
+        <v>673</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="16"/>
       <c r="F26" s="16" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
-        <v>655</v>
+        <v>674</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>656</v>
+        <v>675</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>657</v>
+        <v>676</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="15" t="s">
-        <v>658</v>
+        <v>677</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
-        <v>660</v>
+        <v>679</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="16" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="16"/>
       <c r="F30" s="16" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
-        <v>664</v>
+        <v>683</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>665</v>
+        <v>684</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D31" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
-        <v>666</v>
+        <v>685</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>667</v>
+        <v>686</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D32" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="16"/>
       <c r="F32" s="16" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>668</v>
+        <v>687</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="16"/>
       <c r="F33" s="16" t="s">
-        <v>490</v>
+        <v>512</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>671</v>
+        <v>690</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D34" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="16"/>
       <c r="F34" s="16" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>672</v>
+        <v>691</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D35" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E35" s="16"/>
       <c r="F35" s="16" t="s">
-        <v>673</v>
+        <v>692</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>674</v>
+        <v>693</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>675</v>
+        <v>694</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E36" s="16"/>
       <c r="F36" s="16" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>678</v>
+        <v>697</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="15" t="s">
-        <v>679</v>
+        <v>698</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="16" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="15" t="s">
-        <v>680</v>
+        <v>699</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>681</v>
+        <v>700</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E39" s="16"/>
       <c r="F39" s="16" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
-        <v>682</v>
+        <v>701</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D40" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E40" s="16"/>
       <c r="F40" s="16" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A41" s="15" t="s">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>684</v>
+        <v>703</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>686</v>
+        <v>705</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>687</v>
+        <v>706</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="15" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>688</v>
+        <v>707</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="16" t="s">
-        <v>689</v>
+        <v>708</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>691</v>
+        <v>710</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E43" s="16"/>
       <c r="F43" s="16" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="15" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E44" s="16"/>
       <c r="F44" s="16" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="15" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D45" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="16"/>
       <c r="F45" s="16" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="15" t="s">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D46" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E46" s="16"/>
       <c r="F46" s="16" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="15" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>685</v>
+        <v>704</v>
       </c>
       <c r="D47" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E47" s="16"/>
       <c r="F47" s="16" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
-        <v>693</v>
+        <v>712</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>694</v>
+        <v>713</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>695</v>
+        <v>714</v>
       </c>
       <c r="F48" s="16" t="s">
         <v>289</v>
@@ -10645,96 +10821,96 @@
     </row>
     <row r="49" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>697</v>
+        <v>716</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>698</v>
+        <v>717</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>699</v>
+        <v>718</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A50" s="15" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>700</v>
+        <v>719</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D50" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>701</v>
+        <v>720</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>702</v>
+        <v>721</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="15" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D51" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E51" s="16"/>
       <c r="F51" s="16" t="s">
-        <v>503</v>
+        <v>525</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="15" t="s">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>704</v>
+        <v>723</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D52" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="16"/>
       <c r="F52" s="16" t="s">
-        <v>507</v>
+        <v>529</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="15" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>705</v>
+        <v>724</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D53" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="16"/>
       <c r="F53" s="16" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="25" x14ac:dyDescent="0.35">
@@ -10742,19 +10918,19 @@
         <v>279</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>706</v>
+        <v>725</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>707</v>
+        <v>726</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>708</v>
+        <v>727</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
@@ -10762,55 +10938,57 @@
         <v>133</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>709</v>
+        <v>728</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D55" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>710</v>
+        <v>729</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A56" s="15" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>712</v>
+        <v>731</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="16"/>
+        <v>11</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>732</v>
+      </c>
       <c r="F56" s="16" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="15" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D57" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="16"/>
       <c r="F57" s="16" t="s">
-        <v>511</v>
+        <v>533</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="25" x14ac:dyDescent="0.35">
@@ -10818,16 +10996,16 @@
         <v>272</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D58" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
       <c r="F58" s="16" t="s">
         <v>269</v>
@@ -10835,37 +11013,37 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="15" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="16" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="15" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D60" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="F60" s="16" t="s">
         <v>249</v>
@@ -10873,73 +11051,73 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="15" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E61" s="16"/>
       <c r="F61" s="16" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="15" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D62" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E62" s="16"/>
       <c r="F62" s="16" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D63" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E63" s="16"/>
       <c r="F63" s="16" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A64" s="15" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D64" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="F64" s="16" t="s">
         <v>187</v>
@@ -10947,20 +11125,20 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="15" t="s">
-        <v>518</v>
+        <v>540</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D65" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E65" s="16"/>
       <c r="F65" s="16" t="s">
-        <v>515</v>
+        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
@@ -10968,19 +11146,19 @@
         <v>161</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D66" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="25" x14ac:dyDescent="0.35">
@@ -10988,74 +11166,74 @@
         <v>183</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D67" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="15" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>733</v>
+        <v>753</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D68" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E68" s="16"/>
       <c r="F68" s="16" t="s">
-        <v>499</v>
+        <v>521</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="15" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>734</v>
+        <v>754</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="D69" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>478</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A70" s="15" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="D70" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="F70" s="16"/>
     </row>
@@ -11096,10 +11274,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>18</v>
@@ -11111,15 +11289,15 @@
         <v>42</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="C2" s="15">
         <v>1</v>
@@ -11132,10 +11310,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="C3" s="15">
         <v>1</v>
@@ -11148,10 +11326,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="C4" s="15">
         <v>1</v>
@@ -11164,10 +11342,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="C5" s="15">
         <v>1</v>
@@ -11180,10 +11358,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
       <c r="C6" s="15">
         <v>1</v>
@@ -11196,10 +11374,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="C7" s="15">
         <v>1</v>
@@ -11212,10 +11390,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="C8" s="15">
         <v>2</v>
@@ -11225,15 +11403,15 @@
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="16" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="C9" s="15">
         <v>2</v>
@@ -11243,15 +11421,15 @@
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>759</v>
+        <v>779</v>
       </c>
       <c r="C10" s="15">
         <v>1</v>
@@ -11264,10 +11442,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="C11" s="15">
         <v>1</v>
@@ -11280,10 +11458,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="C12" s="15">
         <v>1</v>
@@ -11298,10 +11476,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="C13" s="15">
         <v>1</v>
@@ -11314,10 +11492,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
       <c r="C14" s="15">
         <v>2</v>
@@ -11327,15 +11505,15 @@
       </c>
       <c r="E14" s="16"/>
       <c r="F14" s="16" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
       <c r="C15" s="15">
         <v>2</v>
@@ -11345,7 +11523,7 @@
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="16" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="25" x14ac:dyDescent="0.35">
@@ -11353,7 +11531,7 @@
         <v>211</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="C16" s="15">
         <v>1</v>
@@ -11362,7 +11540,7 @@
         <v>9</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>208</v>
@@ -11370,10 +11548,10 @@
     </row>
     <row r="17" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="C17" s="15">
         <v>1</v>
@@ -11382,7 +11560,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>296</v>
@@ -11390,10 +11568,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>774</v>
+        <v>794</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="C18" s="15">
         <v>1</v>
@@ -11406,10 +11584,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="C19" s="15">
         <v>1</v>
@@ -11422,10 +11600,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>778</v>
+        <v>798</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>779</v>
+        <v>799</v>
       </c>
       <c r="C20" s="15">
         <v>1</v>
@@ -11438,10 +11616,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="C21" s="15">
         <v>1</v>
@@ -11450,18 +11628,18 @@
         <v>11</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>782</v>
+        <v>802</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>783</v>
+        <v>803</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>784</v>
+        <v>804</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>785</v>
+        <v>805</v>
       </c>
       <c r="C22" s="15">
         <v>1</v>
@@ -11476,10 +11654,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
-        <v>786</v>
+        <v>806</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>787</v>
+        <v>807</v>
       </c>
       <c r="C23" s="15">
         <v>1</v>
@@ -11494,10 +11672,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>788</v>
+        <v>808</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>789</v>
+        <v>809</v>
       </c>
       <c r="C24" s="15">
         <v>1</v>
@@ -11507,15 +11685,15 @@
       </c>
       <c r="E24" s="16"/>
       <c r="F24" s="16" t="s">
-        <v>790</v>
+        <v>810</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>791</v>
+        <v>811</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="C25" s="15">
         <v>1</v>
@@ -11530,10 +11708,10 @@
     </row>
     <row r="26" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="C26" s="15">
         <v>1</v>
@@ -11542,18 +11720,18 @@
         <v>9</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>796</v>
+        <v>816</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="C27" s="15">
         <v>1</v>
@@ -11562,7 +11740,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>798</v>
+        <v>818</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>303</v>
@@ -11570,10 +11748,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="15" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="C28" s="15">
         <v>2</v>
@@ -11583,15 +11761,15 @@
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>801</v>
+        <v>821</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="C29" s="15">
         <v>2</v>
@@ -11601,15 +11779,15 @@
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="16" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="C30" s="15">
         <v>2</v>
@@ -11619,15 +11797,15 @@
       </c>
       <c r="E30" s="16"/>
       <c r="F30" s="16" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="C31" s="15">
         <v>2</v>
@@ -11637,15 +11815,15 @@
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="C32" s="15">
         <v>2</v>
@@ -11655,15 +11833,15 @@
       </c>
       <c r="E32" s="16"/>
       <c r="F32" s="16" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="C33" s="15">
         <v>2</v>
@@ -11673,15 +11851,15 @@
       </c>
       <c r="E33" s="16"/>
       <c r="F33" s="16" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="C34" s="15">
         <v>3</v>
@@ -11691,15 +11869,15 @@
       </c>
       <c r="E34" s="16"/>
       <c r="F34" s="16" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="15" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="C35" s="15">
         <v>3</v>
@@ -11709,15 +11887,15 @@
       </c>
       <c r="E35" s="16"/>
       <c r="F35" s="16" t="s">
-        <v>816</v>
+        <v>836</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>817</v>
+        <v>837</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="C36" s="15">
         <v>1</v>
@@ -11726,7 +11904,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>171</v>
@@ -11734,10 +11912,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>821</v>
+        <v>841</v>
       </c>
       <c r="C37" s="15">
         <v>4</v>
@@ -11747,15 +11925,15 @@
       </c>
       <c r="E37" s="16"/>
       <c r="F37" s="16" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="15" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="C38" s="15">
         <v>4</v>
@@ -11765,15 +11943,15 @@
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="16" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="15" t="s">
-        <v>824</v>
+        <v>844</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="C39" s="15">
         <v>4</v>
@@ -11783,15 +11961,15 @@
       </c>
       <c r="E39" s="16"/>
       <c r="F39" s="16" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="C40" s="15">
         <v>1</v>
@@ -11806,10 +11984,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="15" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="C41" s="15">
         <v>1</v>
@@ -11824,10 +12002,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="15" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="C42" s="15">
         <v>2</v>
@@ -11837,7 +12015,7 @@
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="16" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -11878,102 +12056,102 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>640</v>
+        <v>659</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>12</v>
@@ -11982,21 +12160,21 @@
         <v>47</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>12</v>
@@ -12005,59 +12183,59 @@
         <v>47</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>680</v>
+        <v>699</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>861</v>
+        <v>881</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>862</v>
+        <v>882</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>863</v>
+        <v>883</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>864</v>
+        <v>884</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>865</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>
@@ -12098,12 +12276,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
-        <v>866</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>867</v>
+        <v>887</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -12115,14 +12293,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B3" s="6" t="str">
         <f>COUNTIF(F5:F34,"Verified (live)")&amp;" live-verified, "&amp;COUNTIF(F5:F34,"Verified (simulated)")&amp;" simulated, "&amp;COUNTIF(F5:F34,"Built")&amp;" built, "&amp;COUNTIF(F5:F34,"In progress")&amp;" in progress, "&amp;COUNTIF(F5:F34,"Not started")&amp;" not started, of "&amp;COUNTA(A5:A34)</f>
-        <v>16 live-verified, 11 simulated, 0 built, 0 in progress, 3 not started, of 30</v>
+        <v>16 live-verified, 13 simulated, 1 built, 0 in progress, 0 not started, of 30</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>IF(COUNTIF(F5:F34,"Verified (live)")=COUNTA(A5:A34),"CLOSED","OPEN")</f>
@@ -12134,16 +12312,16 @@
         <v>28</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>35</v>
@@ -12157,726 +12335,734 @@
     </row>
     <row r="5" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>873</v>
+        <v>893</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>175</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>878</v>
+        <v>898</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>183</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>887</v>
+        <v>907</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>306</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>895</v>
+        <v>915</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>896</v>
+        <v>916</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>897</v>
+        <v>917</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>306</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>898</v>
+        <v>918</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>901</v>
+        <v>921</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>902</v>
+        <v>348</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="16"/>
+        <v>913</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>922</v>
+      </c>
       <c r="H10" s="16" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>905</v>
+        <v>925</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>907</v>
+        <v>927</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>908</v>
+        <v>928</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>909</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="50" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>910</v>
+        <v>930</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>231</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>913</v>
+        <v>933</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>914</v>
+        <v>934</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>915</v>
+        <v>935</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>916</v>
+        <v>936</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>238</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>917</v>
+        <v>937</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>918</v>
+        <v>938</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>245</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>922</v>
+        <v>942</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>905</v>
+        <v>925</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>197</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>925</v>
+        <v>945</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>929</v>
+        <v>949</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>204</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>931</v>
+        <v>951</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>933</v>
+        <v>953</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>211</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>936</v>
+        <v>956</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>259</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+        <v>913</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>964</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
-        <v>944</v>
+        <v>966</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>945</v>
+        <v>967</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>266</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>946</v>
+        <v>968</v>
       </c>
       <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>947</v>
+        <v>969</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>948</v>
+        <v>970</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>949</v>
+        <v>971</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>950</v>
+        <v>972</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>951</v>
+        <v>973</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>952</v>
+        <v>974</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>953</v>
+        <v>975</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>954</v>
+        <v>976</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>292</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>955</v>
+        <v>977</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>956</v>
+        <v>978</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A23" s="15" t="s">
+        <v>979</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>957</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>937</v>
-      </c>
       <c r="C23" s="16" t="s">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>299</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>959</v>
+        <v>981</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>960</v>
+        <v>982</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>961</v>
+        <v>983</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>962</v>
+        <v>984</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>252</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>963</v>
+        <v>985</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>964</v>
+        <v>986</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A25" s="15" t="s">
-        <v>965</v>
+        <v>987</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>966</v>
+        <v>988</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>272</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>967</v>
+        <v>989</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>968</v>
+        <v>990</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A26" s="15" t="s">
-        <v>969</v>
+        <v>991</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="D26" s="16" t="s">
         <v>279</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>971</v>
+        <v>993</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>972</v>
+        <v>994</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
-        <v>973</v>
+        <v>995</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>974</v>
+        <v>996</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="16"/>
+        <v>997</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>998</v>
+      </c>
       <c r="H27" s="16" t="s">
-        <v>975</v>
+        <v>999</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A28" s="15" t="s">
-        <v>976</v>
+        <v>1000</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>977</v>
+        <v>1001</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>113</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>978</v>
+        <v>1002</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>979</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="50" x14ac:dyDescent="0.35">
       <c r="A29" s="15" t="s">
-        <v>980</v>
+        <v>1004</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>981</v>
+        <v>1005</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>982</v>
+        <v>1006</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>983</v>
+        <v>1007</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>984</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>985</v>
+        <v>1009</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>986</v>
+        <v>1010</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>327</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>987</v>
+        <v>1011</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>988</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A31" s="15" t="s">
-        <v>989</v>
+        <v>1013</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>990</v>
+        <v>1014</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>334</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>991</v>
+        <v>1015</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>992</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A32" s="15" t="s">
-        <v>993</v>
+        <v>1017</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>994</v>
+        <v>1018</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>995</v>
+        <v>1019</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>996</v>
+        <v>1020</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>997</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>998</v>
+        <v>1022</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>999</v>
+        <v>1023</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>47</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="17" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>1000</v>
+        <v>1024</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>1001</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="25" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>1002</v>
+        <v>1026</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>1003</v>
+        <v>1027</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>147</v>
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="17" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>1004</v>
+        <v>1028</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>1005</v>
+        <v>1029</v>
       </c>
     </row>
   </sheetData>
@@ -12928,33 +13114,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>1006</v>
+        <v>1030</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1007</v>
+        <v>1031</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1008</v>
+        <v>1032</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1009</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>1011</v>
+        <v>1035</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>1013</v>
+        <v>1037</v>
       </c>
       <c r="E2" s="16" t="s">
         <v>47</v>
@@ -12962,33 +13148,33 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1014</v>
+        <v>1038</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1015</v>
+        <v>1039</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>1016</v>
+        <v>1040</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>1017</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1018</v>
+        <v>1042</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>1020</v>
+        <v>1044</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>47</v>
@@ -12996,16 +13182,16 @@
     </row>
     <row r="5" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1021</v>
+        <v>1045</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>47</v>
@@ -13013,16 +13199,16 @@
     </row>
     <row r="6" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>47</v>
@@ -13030,135 +13216,135 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1025</v>
+        <v>1049</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1026</v>
+        <v>1050</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>1027</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1028</v>
+        <v>1052</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>1025</v>
+        <v>1049</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>1027</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1030</v>
+        <v>1054</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1031</v>
+        <v>1055</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1032</v>
+        <v>1056</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>1033</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
-        <v>1034</v>
+        <v>1058</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1035</v>
+        <v>1059</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1036</v>
+        <v>1060</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>1037</v>
+        <v>1061</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>1038</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
-        <v>1034</v>
+        <v>1058</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1039</v>
+        <v>1063</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1036</v>
+        <v>1060</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1040</v>
+        <v>1064</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>1041</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>1034</v>
+        <v>1058</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1036</v>
+        <v>1060</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>1045</v>
+        <v>1069</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>1046</v>
+        <v>1070</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1045</v>
+        <v>1069</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>1047</v>
+        <v>1071</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>1048</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>1045</v>
+        <v>1069</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1045</v>
+        <v>1069</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>1050</v>
+        <v>1074</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>47</v>
@@ -13180,42 +13366,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>1007</v>
+        <v>1031</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1051</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>1011</v>
+        <v>1035</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>1052</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>1053</v>
+        <v>1077</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>1054</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>1055</v>
+        <v>1079</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>1056</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>1058</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -13223,15 +13409,15 @@
         <v>39</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>1059</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>1060</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -13239,23 +13425,23 @@
         <v>32</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>1062</v>
+        <v>1086</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>1063</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
     </row>
   </sheetData>
